--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008520536396819937</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>47376674</v>
+        <v>3785210</v>
       </c>
       <c r="L2" t="n">
-        <v>25398237</v>
+        <v>1754751</v>
       </c>
       <c r="M2" t="n">
-        <v>5726901</v>
+        <v>344664</v>
       </c>
       <c r="N2" t="n">
-        <v>186305</v>
+        <v>9437</v>
       </c>
       <c r="O2" t="n">
-        <v>3412505</v>
+        <v>216300</v>
       </c>
       <c r="P2" t="n">
-        <v>1330106</v>
+        <v>87381</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8373132944107056</v>
+        <v>0.7346441745758057</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6900287270545959</v>
+        <v>0.5253850817680359</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6094176769256592</v>
+        <v>0.4034073650836945</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1736476421356201</v>
+        <v>0.09780287742614746</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6601288318634033</v>
+        <v>0.4603959321975708</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7659487724304199</v>
+        <v>0.5582059621810913</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039522590464157</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>47376674</v>
+        <v>3785210</v>
       </c>
       <c r="E3" t="n">
-        <v>7742244</v>
+        <v>1123174</v>
       </c>
       <c r="F3" t="n">
-        <v>267820</v>
+        <v>66053</v>
       </c>
       <c r="G3" t="n">
-        <v>20908</v>
+        <v>5191</v>
       </c>
       <c r="H3" t="n">
-        <v>24504</v>
+        <v>8040</v>
       </c>
       <c r="I3" t="n">
-        <v>2397</v>
+        <v>1040</v>
       </c>
       <c r="J3" t="n">
-        <v>110765507</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>115936322</v>
+        <v>10060056</v>
       </c>
       <c r="L3" t="n">
-        <v>132873503</v>
+        <v>11490912</v>
       </c>
       <c r="M3" t="n">
-        <v>166595710</v>
+        <v>14961899</v>
       </c>
       <c r="N3" t="n">
-        <v>178703959</v>
+        <v>16238840</v>
       </c>
       <c r="O3" t="n">
-        <v>173204893</v>
+        <v>15649909</v>
       </c>
       <c r="P3" t="n">
-        <v>178041014</v>
+        <v>16152910</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8546411991119385</v>
+        <v>0.7587546706199646</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6998065710067749</v>
+        <v>0.5253893136978149</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5554781556129456</v>
+        <v>0.364962100982666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1890548020601273</v>
+        <v>0.1047310456633568</v>
       </c>
       <c r="V3" t="n">
-        <v>0.607839047908783</v>
+        <v>0.4219845533370972</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6248897910118103</v>
+        <v>0.4505754709243774</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03216441684267991</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8506131</v>
+        <v>1228160</v>
       </c>
       <c r="E4" t="n">
-        <v>25398237</v>
+        <v>1754751</v>
       </c>
       <c r="F4" t="n">
-        <v>1990762</v>
+        <v>271626</v>
       </c>
       <c r="G4" t="n">
-        <v>109997</v>
+        <v>20271</v>
       </c>
       <c r="H4" t="n">
-        <v>255907</v>
+        <v>56480</v>
       </c>
       <c r="I4" t="n">
-        <v>32188</v>
+        <v>8618</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>9205101</v>
+        <v>1367230</v>
       </c>
       <c r="L4" t="n">
-        <v>11409271</v>
+        <v>1585182</v>
       </c>
       <c r="M4" t="n">
-        <v>3670432</v>
+        <v>509718</v>
       </c>
       <c r="N4" t="n">
-        <v>886586</v>
+        <v>87053</v>
       </c>
       <c r="O4" t="n">
-        <v>1756948</v>
+        <v>253513</v>
       </c>
       <c r="P4" t="n">
-        <v>406441</v>
+        <v>69158</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999977946281433</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8458885550498962</v>
+        <v>0.7465047836303711</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6948832273483276</v>
+        <v>0.5253872275352478</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5811991095542908</v>
+        <v>0.3832229673862457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1810239851474762</v>
+        <v>0.1011484637856483</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6329057216644287</v>
+        <v>0.4403541684150696</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6882661581039429</v>
+        <v>0.498649001121521</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>500343</v>
+        <v>103135</v>
       </c>
       <c r="E5" t="n">
-        <v>2986830</v>
+        <v>342631</v>
       </c>
       <c r="F5" t="n">
-        <v>5726901</v>
+        <v>344664</v>
       </c>
       <c r="G5" t="n">
-        <v>267650</v>
+        <v>27672</v>
       </c>
       <c r="H5" t="n">
-        <v>734877</v>
+        <v>107216</v>
       </c>
       <c r="I5" t="n">
-        <v>93238</v>
+        <v>19062</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8057903</v>
+        <v>1203504</v>
       </c>
       <c r="L5" t="n">
-        <v>10894989</v>
+        <v>1585155</v>
       </c>
       <c r="M5" t="n">
-        <v>4582957</v>
+        <v>599719</v>
       </c>
       <c r="N5" t="n">
-        <v>799150</v>
+        <v>80670</v>
       </c>
       <c r="O5" t="n">
-        <v>2201654</v>
+        <v>296278</v>
       </c>
       <c r="P5" t="n">
-        <v>798439</v>
+        <v>106551</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999982714653015</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9044003486633301</v>
+        <v>0.8434007167816162</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8764827251434326</v>
+        <v>0.8068751692771912</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9542940855026245</v>
+        <v>0.9324173331260681</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9906646609306335</v>
+        <v>0.9897829294204712</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9780778884887695</v>
+        <v>0.9665088057518005</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9933275580406189</v>
+        <v>0.9892964959144592</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>152519</v>
+        <v>19497</v>
       </c>
       <c r="E6" t="n">
-        <v>241515</v>
+        <v>25642</v>
       </c>
       <c r="F6" t="n">
-        <v>290424</v>
+        <v>21799</v>
       </c>
       <c r="G6" t="n">
-        <v>186305</v>
+        <v>9437</v>
       </c>
       <c r="H6" t="n">
-        <v>102484</v>
+        <v>11641</v>
       </c>
       <c r="I6" t="n">
-        <v>12144</v>
+        <v>2084</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>43776</v>
+        <v>15256</v>
       </c>
       <c r="E7" t="n">
-        <v>399297</v>
+        <v>83253</v>
       </c>
       <c r="F7" t="n">
-        <v>1036340</v>
+        <v>130844</v>
       </c>
       <c r="G7" t="n">
-        <v>455756</v>
+        <v>28570</v>
       </c>
       <c r="H7" t="n">
-        <v>3412505</v>
+        <v>216300</v>
       </c>
       <c r="I7" t="n">
-        <v>266474</v>
+        <v>38354</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>185</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2332</v>
+        <v>1182</v>
       </c>
       <c r="E8" t="n">
-        <v>39385</v>
+        <v>10482</v>
       </c>
       <c r="F8" t="n">
-        <v>85086</v>
+        <v>19396</v>
       </c>
       <c r="G8" t="n">
-        <v>32275</v>
+        <v>5349</v>
       </c>
       <c r="H8" t="n">
-        <v>639176</v>
+        <v>70136</v>
       </c>
       <c r="I8" t="n">
-        <v>1330106</v>
+        <v>87381</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
